--- a/Collections/EURO/France/#EURO#France#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/France/#EURO#France#Commemorative#[2007-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\France\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE04A66B-DB9A-4FDF-81C6-E547DB800EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A35B951-2B80-4B91-99DA-E789DBD15B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
   <si>
     <t>Year</t>
   </si>
@@ -472,6 +472,12 @@
   </si>
   <si>
     <t>20.000.000</t>
+  </si>
+  <si>
+    <t>320.000</t>
+  </si>
+  <si>
+    <t>80th Anniversary - The Little Prince</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1017,9 +1031,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2569,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="9" t="str">
-        <f t="shared" ref="J43:J44" si="11">IF(OR(AND(I43&gt;1,I43&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J43:J45" si="11">IF(OR(AND(I43&gt;1,I43&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2598,6 +2612,35 @@
         <v>1</v>
       </c>
       <c r="J44" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="7"/>
+      <c r="H45" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I45" s="24">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
@@ -2620,12 +2663,12 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="I3 I6 I10 I12 I14 I17 I23 I26 I8 I21">
-    <cfRule type="containsText" dxfId="27" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6 I3 I10 I12 I14 I17 I23 I26 I8 I21">
-    <cfRule type="colorScale" priority="88">
+  <conditionalFormatting sqref="I3 I6 I10 I12 I14 I17 I23 I26 I8 I21">
+    <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2637,12 +2680,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7 I11 I13 I16 I19 I22 I25 I28 I30">
-    <cfRule type="containsText" dxfId="26" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11 I7 I13 I16 I19 I22 I25 I28 I30">
-    <cfRule type="colorScale" priority="80">
+  <conditionalFormatting sqref="I7 I11 I13 I16 I19 I22 I25 I28 I30">
+    <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2654,11 +2697,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="26" priority="69" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
     <cfRule type="containsText" dxfId="25" priority="67" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2670,13 +2730,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="24" priority="65" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="colorScale" priority="66">
+  <conditionalFormatting sqref="I18">
+    <cfRule type="containsText" dxfId="24" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2687,12 +2747,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+  <conditionalFormatting sqref="I20">
     <cfRule type="containsText" dxfId="23" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
+    <cfRule type="containsText" dxfId="22" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2704,17 +2769,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="containsText" dxfId="22" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I24">
-    <cfRule type="containsText" dxfId="21" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2726,7 +2781,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
+  <conditionalFormatting sqref="I27">
+    <cfRule type="containsText" dxfId="21" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I27">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2738,12 +2798,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
+  <conditionalFormatting sqref="I31">
     <cfRule type="containsText" dxfId="20" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I31">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2755,13 +2815,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="19" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31">
-    <cfRule type="colorScale" priority="54">
+  <conditionalFormatting sqref="I38">
+    <cfRule type="containsText" dxfId="19" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I38))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I38">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2772,12 +2832,80 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="18" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="18" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32">
+    <cfRule type="containsText" dxfId="17" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33">
+    <cfRule type="containsText" dxfId="16" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I35">
+    <cfRule type="containsText" dxfId="15" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I35">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I39">
+    <cfRule type="containsText" dxfId="14" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I39">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2789,13 +2917,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="17" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I29">
-    <cfRule type="colorScale" priority="48">
+  <conditionalFormatting sqref="I36">
+    <cfRule type="containsText" dxfId="13" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I36">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2806,13 +2934,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="16" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
-    <cfRule type="colorScale" priority="46">
+  <conditionalFormatting sqref="I37">
+    <cfRule type="containsText" dxfId="12" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I37">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2823,46 +2951,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="15" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I33">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35">
-    <cfRule type="containsText" dxfId="14" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I39">
-    <cfRule type="containsText" dxfId="13" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I39))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I39">
+  <conditionalFormatting sqref="I34">
+    <cfRule type="containsText" dxfId="11" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2874,13 +2968,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36">
-    <cfRule type="containsText" dxfId="12" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="I40">
+    <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I40">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2891,46 +2985,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I37">
-    <cfRule type="containsText" dxfId="11" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I37">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I34">
-    <cfRule type="containsText" dxfId="10" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I34">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40">
+  <conditionalFormatting sqref="I9">
     <cfRule type="containsText" dxfId="9" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2942,12 +3002,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
+  <conditionalFormatting sqref="I4">
     <cfRule type="containsText" dxfId="8" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2959,13 +3019,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="20">
+  <conditionalFormatting sqref="I41">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I41))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I41">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2976,12 +3036,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I41">
+  <conditionalFormatting sqref="I42">
     <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I41))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I42))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I42">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2993,13 +3053,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I42">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="I43">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I43))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3010,13 +3070,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I43">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="I44">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I44))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I44">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3027,12 +3087,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I44))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I44">
+  <conditionalFormatting sqref="I45">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I45))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/EURO/France/#EURO#France#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/France/#EURO#France#Commemorative#[2007-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\France\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A35B951-2B80-4B91-99DA-E789DBD15B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7C0B0-DFD0-4957-95B1-E8A725768EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -794,14 +794,6 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -809,6 +801,14 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1031,9 +1031,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2638,7 +2638,7 @@
         <v>109</v>
       </c>
       <c r="I45" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="9" t="str">
         <f t="shared" si="11"/>
@@ -2667,7 +2667,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3 I6 I10 I12 I14 I17 I23 I26 I8 I21">
+  <conditionalFormatting sqref="I6 I3 I10 I12 I14 I17 I23 I26 I8 I21">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2684,7 +2684,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7 I11 I13 I16 I19 I22 I25 I28 I30">
+  <conditionalFormatting sqref="I11 I7 I13 I16 I19 I22 I25 I28 I30">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3088,7 +3088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I45">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I45))))</formula>
     </cfRule>
   </conditionalFormatting>
